--- a/data/trans_dic/IQ2606_R2-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IQ2606_R2-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78,85%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>76,65%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>97,19%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>80,91%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>70,46%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>94,99%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>78,85%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,65%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,87; 86,62</t>
+          <t>71,56; 84,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>62,96; 76,45</t>
+          <t>69,8; 82,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>81,56; 100,0</t>
+          <t>87,28; 100,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72,19; 84,52</t>
+          <t>75,26; 85,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,04; 83,09</t>
+          <t>62,05; 76,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,27; 100,0</t>
+          <t>84,85; 100,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,47; 83,93</t>
+          <t>75,5; 84,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>68,94; 78,08</t>
+          <t>68,93; 77,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>89,75; 98,92</t>
+          <t>89,78; 98,92</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>68,73%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86,84%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>72,84%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>79,09%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>97,19%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>68,06; 77,46</t>
+          <t>63,89; 73,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>74,26; 82,95</t>
+          <t>77,87; 85,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90,77; 99,54</t>
+          <t>77,04; 93,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,81; 73,72</t>
+          <t>67,87; 77,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,16; 86,21</t>
+          <t>74,46; 83,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,62; 93,32</t>
+          <t>88,91; 98,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,19; 73,95</t>
+          <t>67,08; 74,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,83; 83,71</t>
+          <t>77,77; 83,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85,65; 95,3</t>
+          <t>84,61; 94,93</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>52,68%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72,31%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>89,31%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>57,14%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>76,23%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>77,35%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52,68%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,31%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50,21; 63,48</t>
+          <t>45,93; 59,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,69; 81,06</t>
+          <t>66,71; 77,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,12; 87,65</t>
+          <t>80,74; 94,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46,11; 59,27</t>
+          <t>50,24; 63,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,63; 77,94</t>
+          <t>70,52; 81,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78,97; 94,74</t>
+          <t>64,4; 86,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,31; 59,48</t>
+          <t>50,09; 59,45</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>69,87; 77,81</t>
+          <t>70,6; 78,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>76,75; 90,2</t>
+          <t>76,23; 90,03</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31,08%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>59,37%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>80,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>38,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>64,05%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>76,96%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>59,37%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>79,02%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,17; 44,16</t>
+          <t>26,15; 37,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,73; 69,78</t>
+          <t>52,99; 65,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64,15; 85,28</t>
+          <t>71,14; 87,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,01; 37,05</t>
+          <t>31,9; 44,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>52,66; 65,69</t>
+          <t>58,16; 70,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,81; 87,82</t>
+          <t>66,56; 85,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>30,58; 38,88</t>
+          <t>30,21; 38,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>57,44; 65,99</t>
+          <t>57,26; 66,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,87; 84,84</t>
+          <t>71,69; 84,68</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57,57%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>62,12%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>73,05%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>57,57%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,02; 65,05</t>
+          <t>54,13; 60,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,32; 75,94</t>
+          <t>70,58; 76,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,18; 88,21</t>
+          <t>80,69; 89,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54,57; 60,63</t>
+          <t>58,64; 64,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,62; 75,96</t>
+          <t>69,98; 75,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,75; 89,91</t>
+          <t>77,03; 87,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,72; 62,13</t>
+          <t>57,37; 61,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,07; 75,01</t>
+          <t>71,28; 75,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,58; 87,88</t>
+          <t>80,46; 87,75</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>93497</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>89411</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10853</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>101690</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>85130</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13063</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>93497</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>89411</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26992</t>
+          <t>23002</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>94102; 108868</t>
+          <t>84849; 100253</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>76064; 92372</t>
+          <t>81417; 95827</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11216; 13752</t>
+          <t>9746; 11166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>85603; 100216</t>
+          <t>94592; 107961</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>81700; 96930</t>
+          <t>74967; 91840</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12202; 14310</t>
+          <t>10801; 12729</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>184339; 205004</t>
+          <t>184409; 205807</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>163714; 185408</t>
+          <t>163695; 184447</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25185; 27758</t>
+          <t>21452; 23638</t>
         </is>
       </c>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>250</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>264</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>184880</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>211981</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>34283</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>172095</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>166499</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33375</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184880</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>211981</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>63686</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>160787; 183006</t>
+          <t>171848; 197210</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>156321; 174629</t>
+          <t>200942; 220748</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31169; 34181</t>
+          <t>30416; 36855</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>171648; 198296</t>
+          <t>160332; 183697</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>201702; 222486</t>
+          <t>156754; 175955</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34296; 41774</t>
+          <t>27204; 30262</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>339471; 373620</t>
+          <t>338898; 374004</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>364707; 392266</t>
+          <t>364428; 393280</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67751; 75388</t>
+          <t>59291; 66527</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>209</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>83543</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>135867</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>47595</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>89386</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>144001</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>30946</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>83543</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>135867</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49735</t>
+          <t>29512</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>80681</t>
+          <t>77107</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78546; 99303</t>
+          <t>72827; 93595</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>133541; 153130</t>
+          <t>125349; 145677</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25654; 35066</t>
+          <t>43028; 50604</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>73120; 93987</t>
+          <t>78592; 98972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>125199; 146456</t>
+          <t>133217; 153499</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44158; 52979</t>
+          <t>24764; 33419</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>158481; 187374</t>
+          <t>157777; 187276</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>263266; 293205</t>
+          <t>266025; 294486</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>73618; 86527</t>
+          <t>69939; 82602</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55731</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>103336</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>60075</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>65264</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>110996</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>41843</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>55731</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>103336</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>43877</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>103785</t>
+          <t>103952</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55122; 75664</t>
+          <t>46898; 67898</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>100053; 120937</t>
+          <t>92226; 113765</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34879; 46366</t>
+          <t>52945; 65221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46641; 66445</t>
+          <t>54662; 75863</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>91662; 114333</t>
+          <t>100787; 121960</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54364; 67428</t>
+          <t>38028; 48661</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>107221; 136350</t>
+          <t>105942; 135321</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>199504; 229199</t>
+          <t>198879; 230107</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>95568; 111274</t>
+          <t>94316; 111405</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>186</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>417652</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>540595</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>152806</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>428434</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>506627</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>119227</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>417652</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>540595</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>164355</t>
+          <t>114941</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>267748</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>407089; 448689</t>
+          <t>392687; 437154</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>487730; 526672</t>
+          <t>519925; 560415</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111389; 125669</t>
+          <t>143923; 160044</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>395913; 439847</t>
+          <t>404431; 447552</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>520202; 559587</t>
+          <t>485312; 524695</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>154849; 172418</t>
+          <t>107006; 121901</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>816773; 879233</t>
+          <t>811897; 874003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1016482; 1072821</t>
+          <t>1019468; 1074166</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>272672; 293736</t>
+          <t>255275; 278403</t>
         </is>
       </c>
     </row>
